--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>543000</v>
+        <v>541000</v>
       </c>
       <c r="C419" t="n">
-        <v>134151</v>
+        <v>308163</v>
       </c>
       <c r="D419" t="n">
-        <v>488944</v>
+        <v>489405</v>
       </c>
       <c r="E419" t="n">
-        <v>543807</v>
+        <v>543731</v>
       </c>
       <c r="F419" t="n">
-        <v>541331</v>
+        <v>541112</v>
       </c>
       <c r="G419" t="n">
-        <v>524694</v>
+        <v>524749</v>
       </c>
       <c r="H419" t="n">
-        <v>1.504876616587657</v>
+        <v>1.505139185273238</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>1.505139185273238</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>533000</v>
+      </c>
+      <c r="C420" t="n">
+        <v>279513</v>
+      </c>
+      <c r="D420" t="n">
+        <v>493163</v>
+      </c>
+      <c r="E420" t="n">
+        <v>549809</v>
+      </c>
+      <c r="F420" t="n">
+        <v>541461</v>
+      </c>
+      <c r="G420" t="n">
+        <v>528144</v>
+      </c>
+      <c r="H420" t="n">
+        <v>1.521346834137749</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>535500</v>
+        <v>529000</v>
       </c>
       <c r="C421" t="n">
-        <v>27426</v>
+        <v>201615</v>
       </c>
       <c r="D421" t="n">
-        <v>494523</v>
+        <v>494838</v>
       </c>
       <c r="E421" t="n">
-        <v>549766</v>
+        <v>549359</v>
       </c>
       <c r="F421" t="n">
-        <v>539303</v>
+        <v>537747</v>
       </c>
       <c r="G421" t="n">
-        <v>527864</v>
+        <v>527315</v>
       </c>
       <c r="H421" t="n">
-        <v>1.520010120829335</v>
+        <v>1.517389207949625</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>1.517389207949625</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>521000</v>
+      </c>
+      <c r="C422" t="n">
+        <v>362337</v>
+      </c>
+      <c r="D422" t="n">
+        <v>496032</v>
+      </c>
+      <c r="E422" t="n">
+        <v>548299</v>
+      </c>
+      <c r="F422" t="n">
+        <v>531798</v>
+      </c>
+      <c r="G422" t="n">
+        <v>525376</v>
+      </c>
+      <c r="H422" t="n">
+        <v>1.508132468288864</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>1.508132468288864</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>533000</v>
+      </c>
+      <c r="C423" t="n">
+        <v>315615</v>
+      </c>
+      <c r="D423" t="n">
+        <v>501974</v>
+      </c>
+      <c r="E423" t="n">
+        <v>549129</v>
+      </c>
+      <c r="F423" t="n">
+        <v>531167</v>
+      </c>
+      <c r="G423" t="n">
+        <v>527423</v>
+      </c>
+      <c r="H423" t="n">
+        <v>1.517904797368584</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>1.517904797368584</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>511000</v>
+      </c>
+      <c r="C424" t="n">
+        <v>349372</v>
+      </c>
+      <c r="D424" t="n">
+        <v>506775</v>
+      </c>
+      <c r="E424" t="n">
+        <v>547400</v>
+      </c>
+      <c r="F424" t="n">
+        <v>524488</v>
+      </c>
+      <c r="G424" t="n">
+        <v>526221</v>
+      </c>
+      <c r="H424" t="n">
+        <v>1.512166478094611</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>1.512166478094611</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>515000</v>
+      </c>
+      <c r="C425" t="n">
+        <v>236123</v>
+      </c>
+      <c r="D425" t="n">
+        <v>518457</v>
+      </c>
+      <c r="E425" t="n">
+        <v>542885</v>
+      </c>
+      <c r="F425" t="n">
+        <v>521334</v>
+      </c>
+      <c r="G425" t="n">
+        <v>527559</v>
+      </c>
+      <c r="H425" t="n">
+        <v>1.518554058118385</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>1.518554058118385</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>517000</v>
+      </c>
+      <c r="C426" t="n">
+        <v>193974</v>
+      </c>
+      <c r="D426" t="n">
+        <v>518439</v>
+      </c>
+      <c r="E426" t="n">
+        <v>539890</v>
+      </c>
+      <c r="F426" t="n">
+        <v>519697</v>
+      </c>
+      <c r="G426" t="n">
+        <v>526009</v>
+      </c>
+      <c r="H426" t="n">
+        <v>1.511154395161098</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>529000</v>
+      </c>
+      <c r="C427" t="n">
+        <v>227965</v>
+      </c>
+      <c r="D427" t="n">
+        <v>518584</v>
+      </c>
+      <c r="E427" t="n">
+        <v>539643</v>
+      </c>
+      <c r="F427" t="n">
+        <v>520943</v>
+      </c>
+      <c r="G427" t="n">
+        <v>526390</v>
+      </c>
+      <c r="H427" t="n">
+        <v>1.51297328005576</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>1.51297328005576</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>575000</v>
+      </c>
+      <c r="C428" t="n">
+        <v>624962</v>
+      </c>
+      <c r="D428" t="n">
+        <v>529571</v>
+      </c>
+      <c r="E428" t="n">
+        <v>542790</v>
+      </c>
+      <c r="F428" t="n">
+        <v>539308</v>
+      </c>
+      <c r="G428" t="n">
+        <v>537223</v>
+      </c>
+      <c r="H428" t="n">
+        <v>1.564689763163046</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>1.564689763163046</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>562000</v>
+      </c>
+      <c r="C429" t="n">
+        <v>327016</v>
+      </c>
+      <c r="D429" t="n">
+        <v>533376</v>
+      </c>
+      <c r="E429" t="n">
+        <v>543875</v>
+      </c>
+      <c r="F429" t="n">
+        <v>550059</v>
+      </c>
+      <c r="G429" t="n">
+        <v>542437</v>
+      </c>
+      <c r="H429" t="n">
+        <v>1.58958127455614</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>1.58958127455614</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>569000</v>
+      </c>
+      <c r="C430" t="n">
+        <v>674883</v>
+      </c>
+      <c r="D430" t="n">
+        <v>534857</v>
+      </c>
+      <c r="E430" t="n">
+        <v>547101</v>
+      </c>
+      <c r="F430" t="n">
+        <v>560339</v>
+      </c>
+      <c r="G430" t="n">
+        <v>547432</v>
+      </c>
+      <c r="H430" t="n">
+        <v>1.61342728518301</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>1.61342728518301</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>561000</v>
+      </c>
+      <c r="C431" t="n">
+        <v>544492</v>
+      </c>
+      <c r="D431" t="n">
+        <v>540470</v>
+      </c>
+      <c r="E431" t="n">
+        <v>544369</v>
+      </c>
+      <c r="F431" t="n">
+        <v>563993</v>
+      </c>
+      <c r="G431" t="n">
+        <v>549611</v>
+      </c>
+      <c r="H431" t="n">
+        <v>1.623829779108126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>1.623829779108126</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>560000</v>
+      </c>
+      <c r="C432" t="n">
+        <v>669905</v>
+      </c>
+      <c r="D432" t="n">
+        <v>542377</v>
+      </c>
+      <c r="E432" t="n">
+        <v>545981</v>
+      </c>
+      <c r="F432" t="n">
+        <v>565859</v>
+      </c>
+      <c r="G432" t="n">
+        <v>551406</v>
+      </c>
+      <c r="H432" t="n">
+        <v>1.632399066210275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>1.632399066210275</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>591000</v>
+      </c>
+      <c r="C433" t="n">
+        <v>852557</v>
+      </c>
+      <c r="D433" t="n">
+        <v>545676</v>
+      </c>
+      <c r="E433" t="n">
+        <v>552035</v>
+      </c>
+      <c r="F433" t="n">
+        <v>570982</v>
+      </c>
+      <c r="G433" t="n">
+        <v>556231</v>
+      </c>
+      <c r="H433" t="n">
+        <v>1.655433500899894</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>1.655433500899894</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>540000</v>
+      </c>
+      <c r="C434" t="n">
+        <v>830836</v>
+      </c>
+      <c r="D434" t="n">
+        <v>545400</v>
+      </c>
+      <c r="E434" t="n">
+        <v>550965</v>
+      </c>
+      <c r="F434" t="n">
+        <v>564599</v>
+      </c>
+      <c r="G434" t="n">
+        <v>553655</v>
+      </c>
+      <c r="H434" t="n">
+        <v>1.643135738462493</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>1.643135738462493</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>530000</v>
+      </c>
+      <c r="C435" t="n">
+        <v>511360</v>
+      </c>
+      <c r="D435" t="n">
+        <v>544953</v>
+      </c>
+      <c r="E435" t="n">
+        <v>549841</v>
+      </c>
+      <c r="F435" t="n">
+        <v>558538</v>
+      </c>
+      <c r="G435" t="n">
+        <v>551111</v>
+      </c>
+      <c r="H435" t="n">
+        <v>1.630990743260339</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>1.630990743260339</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>592000</v>
+      </c>
+      <c r="C436" t="n">
+        <v>1005402</v>
+      </c>
+      <c r="D436" t="n">
+        <v>550476</v>
+      </c>
+      <c r="E436" t="n">
+        <v>555576</v>
+      </c>
+      <c r="F436" t="n">
+        <v>566885</v>
+      </c>
+      <c r="G436" t="n">
+        <v>557646</v>
+      </c>
+      <c r="H436" t="n">
+        <v>1.662188677083483</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>1.662188677083483</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>556000</v>
+      </c>
+      <c r="C437" t="n">
+        <v>669956</v>
+      </c>
+      <c r="D437" t="n">
+        <v>551786</v>
+      </c>
+      <c r="E437" t="n">
+        <v>555608</v>
+      </c>
+      <c r="F437" t="n">
+        <v>566192</v>
+      </c>
+      <c r="G437" t="n">
+        <v>557862</v>
+      </c>
+      <c r="H437" t="n">
+        <v>1.663219855921401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>1.663219855921401</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>554000</v>
+      </c>
+      <c r="C438" t="n">
+        <v>526912</v>
+      </c>
+      <c r="D438" t="n">
+        <v>553008</v>
+      </c>
+      <c r="E438" t="n">
+        <v>556208</v>
+      </c>
+      <c r="F438" t="n">
+        <v>558413</v>
+      </c>
+      <c r="G438" t="n">
+        <v>555876</v>
+      </c>
+      <c r="H438" t="n">
+        <v>1.653738739383871</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>1.653738739383871</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>512000</v>
+      </c>
+      <c r="C439" t="n">
+        <v>506296</v>
+      </c>
+      <c r="D439" t="n">
+        <v>551901</v>
+      </c>
+      <c r="E439" t="n">
+        <v>554416</v>
+      </c>
+      <c r="F439" t="n">
+        <v>555866</v>
+      </c>
+      <c r="G439" t="n">
+        <v>554061</v>
+      </c>
+      <c r="H439" t="n">
+        <v>1.645073972759692</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>1.645073972759692</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>490500</v>
+      </c>
+      <c r="C440" t="n">
+        <v>631720</v>
+      </c>
+      <c r="D440" t="n">
+        <v>549901</v>
+      </c>
+      <c r="E440" t="n">
+        <v>551501</v>
+      </c>
+      <c r="F440" t="n">
+        <v>547464</v>
+      </c>
+      <c r="G440" t="n">
+        <v>549622</v>
+      </c>
+      <c r="H440" t="n">
+        <v>1.623882292845242</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>1.623882292845242</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>483500</v>
+      </c>
+      <c r="C441" t="n">
+        <v>483970</v>
+      </c>
+      <c r="D441" t="n">
+        <v>550458</v>
+      </c>
+      <c r="E441" t="n">
+        <v>548270</v>
+      </c>
+      <c r="F441" t="n">
+        <v>520597</v>
+      </c>
+      <c r="G441" t="n">
+        <v>539775</v>
+      </c>
+      <c r="H441" t="n">
+        <v>1.576872950174011</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>1.576872950174011</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>508000</v>
+      </c>
+      <c r="C442" t="n">
+        <v>464050</v>
+      </c>
+      <c r="D442" t="n">
+        <v>548409</v>
+      </c>
+      <c r="E442" t="n">
+        <v>546515</v>
+      </c>
+      <c r="F442" t="n">
+        <v>509282</v>
+      </c>
+      <c r="G442" t="n">
+        <v>534735</v>
+      </c>
+      <c r="H442" t="n">
+        <v>1.552812110622574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>1.552812110622574</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>534000</v>
+      </c>
+      <c r="C443" t="n">
+        <v>436469</v>
+      </c>
+      <c r="D443" t="n">
+        <v>547509</v>
+      </c>
+      <c r="E443" t="n">
+        <v>546403</v>
+      </c>
+      <c r="F443" t="n">
+        <v>504218</v>
+      </c>
+      <c r="G443" t="n">
+        <v>532710</v>
+      </c>
+      <c r="H443" t="n">
+        <v>1.543144809017086</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>1.543144809017086</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>538000</v>
+      </c>
+      <c r="C444" t="n">
+        <v>1110433</v>
+      </c>
+      <c r="D444" t="n">
+        <v>546960</v>
+      </c>
+      <c r="E444" t="n">
+        <v>546667</v>
+      </c>
+      <c r="F444" t="n">
+        <v>514956</v>
+      </c>
+      <c r="G444" t="n">
+        <v>536194</v>
+      </c>
+      <c r="H444" t="n">
+        <v>1.559777341754627</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성SDI_일별_기준주가.xlsx
+++ b/data/삼성SDI_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>1.559777341754627</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>543000</v>
+      </c>
+      <c r="C445" t="n">
+        <v>754364</v>
+      </c>
+      <c r="D445" t="n">
+        <v>546811</v>
+      </c>
+      <c r="E445" t="n">
+        <v>547058</v>
+      </c>
+      <c r="F445" t="n">
+        <v>526221</v>
+      </c>
+      <c r="G445" t="n">
+        <v>540030</v>
+      </c>
+      <c r="H445" t="n">
+        <v>1.578090314079888</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
